--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>HDKSOE</t>
@@ -70,25 +73,25 @@
     <t>Hanwha Ocean</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>009540.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
     <t>010620.KS</t>
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -513,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>432000</v>
+        <v>27050</v>
       </c>
       <c r="E2">
-        <v>48.5</v>
+        <v>61.5</v>
       </c>
       <c r="F2">
-        <v>5.37</v>
+        <v>10.41</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K2">
-        <v>59.7</v>
+        <v>62.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,10 +546,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -560,28 +563,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>108500</v>
+        <v>447500</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>60.4</v>
       </c>
       <c r="F3">
-        <v>0.65</v>
+        <v>8.35</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>80</v>
+      </c>
+      <c r="I3">
         <v>70</v>
       </c>
-      <c r="I3">
-        <v>80</v>
-      </c>
       <c r="J3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>53.7</v>
+        <v>60.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,10 +593,10 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -607,40 +610,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>25450</v>
+        <v>115200</v>
       </c>
       <c r="E4">
-        <v>44.4</v>
+        <v>39.6</v>
       </c>
       <c r="F4">
-        <v>3.46</v>
+        <v>8.58</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I4">
+        <v>76</v>
+      </c>
+      <c r="J4">
         <v>70</v>
       </c>
-      <c r="J4">
-        <v>90</v>
-      </c>
       <c r="K4">
-        <v>52.7</v>
+        <v>50.8</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -657,7 +660,7 @@
         <v>223000</v>
       </c>
       <c r="E5">
-        <v>26.8</v>
+        <v>25.7</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -666,28 +669,28 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I5">
         <v>70</v>
       </c>
       <c r="J5">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>46.7</v>
+        <v>45.4</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>52.28493729186943</v>
+        <v>48.11568981226033</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -516,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>27050</v>
+        <v>26400</v>
       </c>
       <c r="E2">
-        <v>61.5</v>
+        <v>49.6</v>
       </c>
       <c r="F2">
-        <v>10.41</v>
+        <v>6.88</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>70</v>
       </c>
       <c r="I2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K2">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,37 +563,37 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>447500</v>
+        <v>446000</v>
       </c>
       <c r="E3">
-        <v>60.4</v>
+        <v>54.9</v>
       </c>
       <c r="F3">
-        <v>8.35</v>
+        <v>5.44</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I3">
         <v>70</v>
       </c>
       <c r="J3">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>115200</v>
+        <v>113100</v>
       </c>
       <c r="E4">
-        <v>39.6</v>
+        <v>34.1</v>
       </c>
       <c r="F4">
-        <v>8.58</v>
+        <v>4.53</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I4">
         <v>76</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -660,25 +660,25 @@
         <v>223000</v>
       </c>
       <c r="E5">
-        <v>25.7</v>
+        <v>40.9</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5">
+        <v>70</v>
+      </c>
+      <c r="I5">
         <v>66</v>
       </c>
-      <c r="I5">
-        <v>70</v>
-      </c>
       <c r="J5">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K5">
-        <v>45.4</v>
+        <v>46.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>48.11568981226033</v>
+        <v>46.17217538625081</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,25 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-10</t>
+    <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>HDKSOE</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
-    <t>HDKSOE</t>
-  </si>
-  <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>009540.KS</t>
+  </si>
+  <si>
     <t>010140.KS</t>
-  </si>
-  <si>
-    <t>009540.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
@@ -516,28 +516,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>26400</v>
+        <v>449500</v>
       </c>
       <c r="E2">
-        <v>49.6</v>
+        <v>56.9</v>
       </c>
       <c r="F2">
-        <v>6.88</v>
+        <v>4.05</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>62.3</v>
+        <v>61.4</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,7 +546,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
@@ -563,37 +563,37 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>446000</v>
+        <v>26300</v>
       </c>
       <c r="E3">
-        <v>54.9</v>
+        <v>59.4</v>
       </c>
       <c r="F3">
-        <v>5.44</v>
+        <v>3.34</v>
       </c>
       <c r="G3">
         <v>60</v>
       </c>
       <c r="H3">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="K3">
-        <v>59.9</v>
+        <v>61.4</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O3" t="s">
         <v>27</v>
@@ -610,28 +610,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>113100</v>
+        <v>114100</v>
       </c>
       <c r="E4">
-        <v>34.1</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>4.53</v>
+        <v>5.16</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I4">
         <v>76</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>53.3</v>
+        <v>56.6</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -640,7 +640,7 @@
         <v>26</v>
       </c>
       <c r="N4">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O4" t="s">
         <v>27</v>
@@ -660,7 +660,7 @@
         <v>223000</v>
       </c>
       <c r="E5">
-        <v>40.9</v>
+        <v>63.6</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -669,16 +669,16 @@
         <v>20</v>
       </c>
       <c r="H5">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="I5">
         <v>66</v>
       </c>
       <c r="J5">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K5">
-        <v>46.3</v>
+        <v>46.6</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="N5">
-        <v>46.17217538625081</v>
+        <v>47.37006702605126</v>
       </c>
       <c r="O5" t="s">
         <v>27</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>날짜</t>
   </si>
@@ -61,37 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-15</t>
+    <t>2025-12-29</t>
+  </si>
+  <si>
+    <t>Hanwha Ocean</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
-    <t>Hanwha Ocean</t>
-  </si>
-  <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>042660.KS</t>
+  </si>
+  <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>009540.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
-    <t>042660.KS</t>
-  </si>
-  <si>
     <t>010620.KS</t>
   </si>
   <si>
     <t>Pattern</t>
-  </si>
-  <si>
-    <t>📈 매수 관찰 구간입니다.</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
@@ -516,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>449500</v>
+        <v>115600</v>
       </c>
       <c r="E2">
-        <v>56.9</v>
+        <v>51.8</v>
       </c>
       <c r="F2">
-        <v>4.05</v>
+        <v>5.57</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>61.4</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -546,10 +543,10 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -563,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>26300</v>
+        <v>24600</v>
       </c>
       <c r="E3">
-        <v>59.4</v>
+        <v>43.3</v>
       </c>
       <c r="F3">
-        <v>3.34</v>
+        <v>-3.15</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K3">
-        <v>61.4</v>
+        <v>48</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -593,10 +590,10 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>47.37006702605126</v>
+        <v>51.940834218365</v>
       </c>
       <c r="O3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -610,40 +607,40 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>114100</v>
+        <v>410500</v>
       </c>
       <c r="E4">
-        <v>43</v>
+        <v>38.7</v>
       </c>
       <c r="F4">
-        <v>5.16</v>
+        <v>-2.49</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I4">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>56.6</v>
+        <v>47.8</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
       </c>
       <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
+        <v>51.940834218365</v>
+      </c>
+      <c r="O4" t="s">
         <v>26</v>
-      </c>
-      <c r="N4">
-        <v>47.37006702605126</v>
-      </c>
-      <c r="O4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -660,37 +657,37 @@
         <v>223000</v>
       </c>
       <c r="E5">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I5">
+        <v>60</v>
+      </c>
+      <c r="J5">
         <v>66</v>
       </c>
-      <c r="J5">
-        <v>70</v>
-      </c>
       <c r="K5">
-        <v>46.6</v>
+        <v>42.6</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
       </c>
       <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
+        <v>51.940834218365</v>
+      </c>
+      <c r="O5" t="s">
         <v>26</v>
-      </c>
-      <c r="N5">
-        <v>47.37006702605126</v>
-      </c>
-      <c r="O5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,28 +61,28 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2025-12-29</t>
+    <t>2026-01-05</t>
   </si>
   <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
+    <t>HDKSOE</t>
+  </si>
+  <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
-    <t>HDKSOE</t>
-  </si>
-  <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
     <t>042660.KS</t>
   </si>
   <si>
+    <t>009540.KS</t>
+  </si>
+  <si>
     <t>010140.KS</t>
-  </si>
-  <si>
-    <t>009540.KS</t>
   </si>
   <si>
     <t>010620.KS</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>115600</v>
+        <v>114700</v>
       </c>
       <c r="E2">
-        <v>51.8</v>
+        <v>52.6</v>
       </c>
       <c r="F2">
-        <v>5.57</v>
+        <v>-7.05</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="I2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J2">
         <v>63</v>
       </c>
       <c r="K2">
-        <v>58.8</v>
+        <v>55.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>24600</v>
+        <v>393500</v>
       </c>
       <c r="E3">
-        <v>43.3</v>
+        <v>31.3</v>
       </c>
       <c r="F3">
-        <v>-3.15</v>
+        <v>-8.91</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>48</v>
+        <v>44.7</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>410500</v>
+        <v>24150</v>
       </c>
       <c r="E4">
-        <v>38.7</v>
+        <v>37.3</v>
       </c>
       <c r="F4">
-        <v>-2.49</v>
+        <v>-3.98</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K4">
-        <v>47.8</v>
+        <v>40.7</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>42.6</v>
+        <v>39.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>51.940834218365</v>
+        <v>41.50472307187444</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-05</t>
+    <t>2026-01-07</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>Hanwha Ocean</t>
@@ -70,19 +73,16 @@
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>042660.KS</t>
   </si>
   <si>
     <t>009540.KS</t>
-  </si>
-  <si>
-    <t>010140.KS</t>
   </si>
   <si>
     <t>010620.KS</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>114700</v>
+        <v>25700</v>
       </c>
       <c r="E2">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="F2">
-        <v>-7.05</v>
+        <v>4.47</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I2">
         <v>70</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K2">
-        <v>55.5</v>
+        <v>56.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>393500</v>
+        <v>122800</v>
       </c>
       <c r="E3">
-        <v>31.3</v>
+        <v>59.8</v>
       </c>
       <c r="F3">
-        <v>-8.91</v>
+        <v>6.23</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>60</v>
+      </c>
+      <c r="I3">
+        <v>53</v>
+      </c>
+      <c r="J3">
         <v>63</v>
       </c>
-      <c r="I3">
-        <v>73</v>
-      </c>
-      <c r="J3">
-        <v>70</v>
-      </c>
       <c r="K3">
-        <v>44.7</v>
+        <v>52.7</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>24150</v>
+        <v>421000</v>
       </c>
       <c r="E4">
-        <v>37.3</v>
+        <v>44.2</v>
       </c>
       <c r="F4">
-        <v>-3.98</v>
+        <v>2.56</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J4">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K4">
-        <v>40.7</v>
+        <v>50.5</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -666,16 +666,16 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J5">
         <v>66</v>
       </c>
       <c r="K5">
-        <v>39.5</v>
+        <v>38.9</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>41.50472307187444</v>
+        <v>45.04298008974126</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -513,19 +513,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>25700</v>
+        <v>25300</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>47.5</v>
       </c>
       <c r="F2">
-        <v>4.47</v>
+        <v>2.85</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>70</v>
@@ -534,7 +534,7 @@
         <v>83</v>
       </c>
       <c r="K2">
-        <v>56.5</v>
+        <v>56.6</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,13 +560,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>122800</v>
+        <v>120800</v>
       </c>
       <c r="E3">
-        <v>59.8</v>
+        <v>58</v>
       </c>
       <c r="F3">
-        <v>6.23</v>
+        <v>4.5</v>
       </c>
       <c r="G3">
         <v>60</v>
@@ -581,7 +581,7 @@
         <v>63</v>
       </c>
       <c r="K3">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>421000</v>
+        <v>414500</v>
       </c>
       <c r="E4">
-        <v>44.2</v>
+        <v>41.4</v>
       </c>
       <c r="F4">
-        <v>2.56</v>
+        <v>0.97</v>
       </c>
       <c r="G4">
         <v>30</v>
       </c>
       <c r="H4">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I4">
+        <v>66</v>
+      </c>
+      <c r="J4">
         <v>70</v>
       </c>
-      <c r="J4">
-        <v>73</v>
-      </c>
       <c r="K4">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.04298008974126</v>
+        <v>45.26531441048893</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-07</t>
+    <t>2026-01-08</t>
+  </si>
+  <si>
+    <t>HDKSOE</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
@@ -70,19 +73,16 @@
     <t>Hanwha Ocean</t>
   </si>
   <si>
-    <t>HDKSOE</t>
-  </si>
-  <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>009540.KS</t>
+  </si>
+  <si>
     <t>010140.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
-  </si>
-  <si>
-    <t>009540.KS</t>
   </si>
   <si>
     <t>010620.KS</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>25300</v>
+        <v>424500</v>
       </c>
       <c r="E2">
-        <v>47.5</v>
+        <v>50.8</v>
       </c>
       <c r="F2">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I2">
         <v>70</v>
       </c>
       <c r="J2">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>56.6</v>
+        <v>56.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>120800</v>
+        <v>26350</v>
       </c>
       <c r="E3">
-        <v>58</v>
+        <v>58.9</v>
       </c>
       <c r="F3">
-        <v>4.5</v>
+        <v>9.34</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="K3">
-        <v>52.8</v>
+        <v>54.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>414500</v>
+        <v>129700</v>
       </c>
       <c r="E4">
-        <v>41.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F4">
-        <v>0.97</v>
+        <v>14.17</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="I4">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="K4">
-        <v>49</v>
+        <v>46.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>39</v>
+        <v>38.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>45.26531441048893</v>
+        <v>43.60821037092016</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-08</t>
+    <t>2026-01-11</t>
   </si>
   <si>
     <t>HDKSOE</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>424500</v>
+        <v>447000</v>
       </c>
       <c r="E2">
-        <v>50.8</v>
+        <v>58.6</v>
       </c>
       <c r="F2">
-        <v>4.3</v>
+        <v>13.6</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="J2">
         <v>70</v>
       </c>
       <c r="K2">
-        <v>56.1</v>
+        <v>52.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>26350</v>
+        <v>28650</v>
       </c>
       <c r="E3">
-        <v>58.9</v>
+        <v>71</v>
       </c>
       <c r="F3">
-        <v>9.34</v>
+        <v>18.63</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K3">
-        <v>54.5</v>
+        <v>51.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>129700</v>
+        <v>134400</v>
       </c>
       <c r="E4">
-        <v>70.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F4">
-        <v>14.17</v>
+        <v>17.18</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
         <v>56</v>
       </c>
-      <c r="I4">
-        <v>53</v>
-      </c>
-      <c r="J4">
-        <v>43</v>
-      </c>
       <c r="K4">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>38.5</v>
+        <v>40.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.60821037092016</v>
+        <v>50.40292622392195</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-11</t>
+    <t>2026-01-12</t>
   </si>
   <si>
     <t>HDKSOE</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>447000</v>
+        <v>449000</v>
       </c>
       <c r="E2">
-        <v>58.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F2">
-        <v>13.6</v>
+        <v>11.97</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H2">
         <v>66</v>
       </c>
       <c r="I2">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K2">
-        <v>52.5</v>
+        <v>57.1</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28650</v>
+        <v>28050</v>
       </c>
       <c r="E3">
-        <v>71</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F3">
-        <v>18.63</v>
+        <v>14.72</v>
       </c>
       <c r="G3">
         <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J3">
         <v>70</v>
       </c>
       <c r="K3">
-        <v>51.1</v>
+        <v>55.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>134400</v>
+        <v>146500</v>
       </c>
       <c r="E4">
-        <v>73.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="F4">
-        <v>17.18</v>
+        <v>24.26</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J4">
         <v>56</v>
       </c>
       <c r="K4">
-        <v>47.1</v>
+        <v>48.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.40292622392195</v>
+        <v>50.43822221555986</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -513,13 +513,13 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>449000</v>
+        <v>450500</v>
       </c>
       <c r="E2">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="F2">
-        <v>11.97</v>
+        <v>12.34</v>
       </c>
       <c r="G2">
         <v>60</v>
@@ -534,7 +534,7 @@
         <v>66</v>
       </c>
       <c r="K2">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,13 +560,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28050</v>
+        <v>28150</v>
       </c>
       <c r="E3">
-        <v>71.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F3">
-        <v>14.72</v>
+        <v>15.13</v>
       </c>
       <c r="G3">
         <v>40</v>
@@ -581,7 +581,7 @@
         <v>70</v>
       </c>
       <c r="K3">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,13 +607,13 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>146500</v>
+        <v>145700</v>
       </c>
       <c r="E4">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F4">
-        <v>24.26</v>
+        <v>23.58</v>
       </c>
       <c r="G4">
         <v>40</v>
@@ -628,7 +628,7 @@
         <v>56</v>
       </c>
       <c r="K4">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.43822221555986</v>
+        <v>50.56766494832259</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-12</t>
+    <t>2026-01-13</t>
   </si>
   <si>
     <t>HDKSOE</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>450500</v>
+        <v>458000</v>
       </c>
       <c r="E2">
-        <v>65</v>
+        <v>63.8</v>
       </c>
       <c r="F2">
-        <v>12.34</v>
+        <v>10.63</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
+        <v>56</v>
+      </c>
+      <c r="I2">
         <v>66</v>
-      </c>
-      <c r="I2">
-        <v>60</v>
       </c>
       <c r="J2">
         <v>66</v>
       </c>
       <c r="K2">
-        <v>57.2</v>
+        <v>58.8</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28150</v>
+        <v>28500</v>
       </c>
       <c r="E3">
-        <v>72.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="F3">
-        <v>15.13</v>
+        <v>14.92</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I3">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J3">
         <v>70</v>
       </c>
       <c r="K3">
-        <v>55.2</v>
+        <v>54.6</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>145700</v>
+        <v>147900</v>
       </c>
       <c r="E4">
-        <v>84.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F4">
-        <v>23.58</v>
+        <v>23.46</v>
       </c>
       <c r="G4">
         <v>40</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>48.4</v>
+        <v>51.6</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>40.6</v>
+        <v>39.8</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>50.56766494832259</v>
+        <v>47.98314273412904</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-13</t>
+    <t>2026-01-14</t>
   </si>
   <si>
     <t>HDKSOE</t>
@@ -513,19 +513,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>458000</v>
+        <v>427500</v>
       </c>
       <c r="E2">
-        <v>63.8</v>
+        <v>52.6</v>
       </c>
       <c r="F2">
-        <v>10.63</v>
+        <v>2.27</v>
       </c>
       <c r="G2">
         <v>60</v>
       </c>
       <c r="H2">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I2">
         <v>66</v>
@@ -534,7 +534,7 @@
         <v>66</v>
       </c>
       <c r="K2">
-        <v>58.8</v>
+        <v>57.3</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28500</v>
+        <v>28350</v>
       </c>
       <c r="E3">
-        <v>68</v>
+        <v>69.2</v>
       </c>
       <c r="F3">
-        <v>14.92</v>
+        <v>11.83</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I3">
         <v>63</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>54.6</v>
+        <v>56.1</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,28 +607,28 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>147900</v>
+        <v>142000</v>
       </c>
       <c r="E4">
-        <v>83.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F4">
-        <v>23.46</v>
+        <v>17.16</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H4">
+        <v>63</v>
+      </c>
+      <c r="I4">
         <v>60</v>
-      </c>
-      <c r="I4">
-        <v>63</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>39.8</v>
+        <v>38.3</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>47.98314273412904</v>
+        <v>43.1153238131143</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,25 +61,25 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-14</t>
+    <t>2026-01-17</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
     <t>HD HYUNDAI MIPO</t>
   </si>
   <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>009540.KS</t>
-  </si>
-  <si>
-    <t>010140.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>427500</v>
+        <v>29750</v>
       </c>
       <c r="E2">
-        <v>52.6</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F2">
-        <v>2.27</v>
+        <v>3.84</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>57.3</v>
+        <v>57.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,28 +560,28 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>28350</v>
+        <v>438500</v>
       </c>
       <c r="E3">
-        <v>69.2</v>
+        <v>57.2</v>
       </c>
       <c r="F3">
-        <v>11.83</v>
+        <v>-1.9</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J3">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="K3">
-        <v>56.1</v>
+        <v>53.5</v>
       </c>
       <c r="L3" t="s">
         <v>24</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,13 +607,13 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>142000</v>
+        <v>147000</v>
       </c>
       <c r="E4">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="F4">
-        <v>17.16</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G4">
         <v>50</v>
@@ -622,13 +622,13 @@
         <v>63</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J4">
         <v>60</v>
       </c>
       <c r="K4">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="L4" t="s">
         <v>24</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -675,7 +675,7 @@
         <v>66</v>
       </c>
       <c r="K5">
-        <v>38.3</v>
+        <v>37.5</v>
       </c>
       <c r="L5" t="s">
         <v>24</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>43.1153238131143</v>
+        <v>40.49436870247035</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,7 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-17</t>
+    <t>2026-01-19</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
@@ -513,28 +513,28 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>29750</v>
+        <v>31850</v>
       </c>
       <c r="E2">
-        <v>75.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="F2">
-        <v>3.84</v>
+        <v>13.14</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I2">
         <v>76</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>57.5</v>
+        <v>54.5</v>
       </c>
       <c r="L2" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="N2">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -560,25 +560,25 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>438500</v>
+        <v>444500</v>
       </c>
       <c r="E3">
-        <v>57.2</v>
+        <v>64</v>
       </c>
       <c r="F3">
-        <v>-1.9</v>
+        <v>-1.33</v>
       </c>
       <c r="G3">
         <v>50</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I3">
         <v>66</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K3">
         <v>53.5</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="N3">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O3" t="s">
         <v>26</v>
@@ -607,25 +607,25 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>147000</v>
+        <v>148800</v>
       </c>
       <c r="E4">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F4">
-        <v>9.380000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I4">
         <v>63</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="K4">
         <v>52.3</v>
@@ -637,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="N4">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O4" t="s">
         <v>26</v>
@@ -672,7 +672,7 @@
         <v>56</v>
       </c>
       <c r="J5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K5">
         <v>37.5</v>
@@ -684,7 +684,7 @@
         <v>25</v>
       </c>
       <c r="N5">
-        <v>40.49436870247035</v>
+        <v>40.44495449250464</v>
       </c>
       <c r="O5" t="s">
         <v>26</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,40 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-01-19</t>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
+    <t>Hanwha Ocean</t>
+  </si>
+  <si>
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>Hanwha Ocean</t>
-  </si>
-  <si>
-    <t>HD HYUNDAI MIPO</t>
-  </si>
-  <si>
     <t>010140.KS</t>
   </si>
   <si>
+    <t>042660.KS</t>
+  </si>
+  <si>
     <t>009540.KS</t>
   </si>
   <si>
-    <t>042660.KS</t>
-  </si>
-  <si>
-    <t>010620.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -452,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -510,43 +504,43 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>31850</v>
+        <v>28000</v>
       </c>
       <c r="E2">
-        <v>83.2</v>
+        <v>49.1</v>
       </c>
       <c r="F2">
-        <v>13.14</v>
+        <v>-4.27</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I2">
         <v>76</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
+        <v>20.49503599836755</v>
+      </c>
+      <c r="O2" t="s">
         <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,19 +551,19 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3">
-        <v>444500</v>
+        <v>135400</v>
       </c>
       <c r="E3">
-        <v>64</v>
+        <v>49.8</v>
       </c>
       <c r="F3">
-        <v>-1.33</v>
+        <v>-8.02</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>60</v>
@@ -581,19 +575,19 @@
         <v>70</v>
       </c>
       <c r="K3">
-        <v>53.5</v>
+        <v>41.5</v>
       </c>
       <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>20.49503599836755</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,90 +598,43 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>148800</v>
+        <v>441500</v>
       </c>
       <c r="E4">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="F4">
-        <v>2.13</v>
+        <v>-4.6</v>
       </c>
       <c r="G4">
         <v>50</v>
       </c>
       <c r="H4">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I4">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="J4">
         <v>56</v>
       </c>
       <c r="K4">
-        <v>52.3</v>
+        <v>41.1</v>
       </c>
       <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>20.49503599836755</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5">
-        <v>223000</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>10</v>
-      </c>
-      <c r="H5">
-        <v>53</v>
-      </c>
-      <c r="I5">
-        <v>56</v>
-      </c>
-      <c r="J5">
-        <v>63</v>
-      </c>
-      <c r="K5">
-        <v>37.5</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5">
-        <v>40.44495449250464</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,24 +61,24 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-03</t>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>Hanwha Ocean</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
-    <t>Hanwha Ocean</t>
-  </si>
-  <si>
     <t>HDKSOE</t>
   </si>
   <si>
+    <t>042660.KS</t>
+  </si>
+  <si>
     <t>010140.KS</t>
   </si>
   <si>
-    <t>042660.KS</t>
-  </si>
-  <si>
     <t>009540.KS</t>
   </si>
   <si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>28000</v>
+        <v>121400</v>
       </c>
       <c r="E2">
-        <v>49.1</v>
+        <v>45.5</v>
       </c>
       <c r="F2">
-        <v>-4.27</v>
+        <v>-14.02</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="I2">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="K2">
-        <v>45.5</v>
+        <v>31.3</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>135400</v>
+        <v>26550</v>
       </c>
       <c r="E3">
-        <v>49.8</v>
+        <v>44.8</v>
       </c>
       <c r="F3">
-        <v>-8.02</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="G3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3">
         <v>60</v>
       </c>
       <c r="I3">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K3">
-        <v>41.5</v>
+        <v>31.3</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>441500</v>
+        <v>382000</v>
       </c>
       <c r="E4">
-        <v>63</v>
+        <v>49.9</v>
       </c>
       <c r="F4">
-        <v>-4.6</v>
+        <v>-15.11</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H4">
         <v>53</v>
       </c>
       <c r="I4">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="K4">
-        <v>41.1</v>
+        <v>28.5</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>20.49503599836755</v>
+        <v>4.469434098808478</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -64,31 +64,31 @@
     <t>2026-03-09</t>
   </si>
   <si>
+    <t>SamsungHvyInd</t>
+  </si>
+  <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
     <t>HDKSOE</t>
   </si>
   <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>042660.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
     <t>009540.KS</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
-  </si>
-  <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
     <t>🔴 강한 긴축 / 리스크</t>
@@ -510,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>121400</v>
+        <v>28550</v>
       </c>
       <c r="E2">
-        <v>45.5</v>
+        <v>52</v>
       </c>
       <c r="F2">
-        <v>-14.02</v>
+        <v>-1.38</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="I2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J2">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="K2">
-        <v>31.3</v>
+        <v>34.2</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,28 +557,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>26550</v>
+        <v>123700</v>
       </c>
       <c r="E3">
-        <v>44.8</v>
+        <v>46.6</v>
       </c>
       <c r="F3">
-        <v>-8.289999999999999</v>
+        <v>-12.39</v>
       </c>
       <c r="G3">
         <v>20</v>
       </c>
       <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>56</v>
+      </c>
+      <c r="J3">
         <v>60</v>
       </c>
-      <c r="I3">
-        <v>60</v>
-      </c>
-      <c r="J3">
-        <v>83</v>
-      </c>
       <c r="K3">
-        <v>31.3</v>
+        <v>28.4</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,7 +587,7 @@
         <v>24</v>
       </c>
       <c r="N3">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,13 +604,13 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>382000</v>
+        <v>400000</v>
       </c>
       <c r="E4">
-        <v>49.9</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>-15.11</v>
+        <v>-11.11</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -622,10 +622,10 @@
         <v>53</v>
       </c>
       <c r="J4">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="K4">
-        <v>28.5</v>
+        <v>27.2</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>4.469434098808478</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,37 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-09</t>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>Hanwha Ocean</t>
+  </si>
+  <si>
+    <t>HDKSOE</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
-    <t>Hanwha Ocean</t>
-  </si>
-  <si>
-    <t>HDKSOE</t>
+    <t>042660.KS</t>
+  </si>
+  <si>
+    <t>009540.KS</t>
   </si>
   <si>
     <t>010140.KS</t>
   </si>
   <si>
-    <t>042660.KS</t>
-  </si>
-  <si>
-    <t>009540.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>⛔ 관망하십시오.</t>
+  </si>
+  <si>
     <t>🤏 바닥권 접근 구간입니다.</t>
   </si>
   <si>
-    <t>⛔ 관망하십시오.</t>
-  </si>
-  <si>
-    <t>🔴 강한 긴축 / 리스크</t>
+    <t>🟠 하락 우위 (긴장 구간)</t>
   </si>
 </sst>
 </file>
@@ -510,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>28550</v>
+        <v>122400</v>
       </c>
       <c r="E2">
-        <v>52</v>
+        <v>44.7</v>
       </c>
       <c r="F2">
-        <v>-1.38</v>
+        <v>-9.6</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
+        <v>70</v>
+      </c>
+      <c r="J2">
         <v>56</v>
       </c>
-      <c r="I2">
-        <v>63</v>
-      </c>
-      <c r="J2">
-        <v>86</v>
-      </c>
       <c r="K2">
-        <v>34.2</v>
+        <v>43.7</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,37 +557,37 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>123700</v>
+        <v>393500</v>
       </c>
       <c r="E3">
-        <v>46.6</v>
+        <v>51</v>
       </c>
       <c r="F3">
-        <v>-12.39</v>
+        <v>-10.87</v>
       </c>
       <c r="G3">
         <v>20</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>28.4</v>
+        <v>39.7</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,28 +604,28 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>400000</v>
+        <v>27450</v>
       </c>
       <c r="E4">
-        <v>54</v>
+        <v>47.7</v>
       </c>
       <c r="F4">
-        <v>-11.11</v>
+        <v>-1.96</v>
       </c>
       <c r="G4">
         <v>20</v>
       </c>
       <c r="H4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K4">
-        <v>27.2</v>
+        <v>39.7</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>32.23518188264562</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -510,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>122400</v>
+        <v>124400</v>
       </c>
       <c r="E2">
-        <v>44.7</v>
+        <v>45.8</v>
       </c>
       <c r="F2">
-        <v>-9.6</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="G2">
         <v>20</v>
       </c>
       <c r="H2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I2">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="K2">
-        <v>43.7</v>
+        <v>42.1</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,7 +540,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O2" t="s">
         <v>25</v>
@@ -557,13 +557,13 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>393500</v>
+        <v>403500</v>
       </c>
       <c r="E3">
-        <v>51</v>
+        <v>53.3</v>
       </c>
       <c r="F3">
-        <v>-10.87</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="G3">
         <v>20</v>
@@ -575,7 +575,7 @@
         <v>60</v>
       </c>
       <c r="J3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K3">
         <v>39.7</v>
@@ -587,7 +587,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O3" t="s">
         <v>25</v>
@@ -604,13 +604,13 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>27450</v>
+        <v>27850</v>
       </c>
       <c r="E4">
-        <v>47.7</v>
+        <v>49</v>
       </c>
       <c r="F4">
-        <v>-1.96</v>
+        <v>-0.54</v>
       </c>
       <c r="G4">
         <v>20</v>
@@ -619,13 +619,13 @@
         <v>60</v>
       </c>
       <c r="I4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="J4">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K4">
-        <v>39.7</v>
+        <v>38.1</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -634,7 +634,7 @@
         <v>24</v>
       </c>
       <c r="N4">
-        <v>32.23518188264562</v>
+        <v>32.42054265786911</v>
       </c>
       <c r="O4" t="s">
         <v>25</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-10</t>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>Hanwha Ocean</t>
@@ -70,7 +73,7 @@
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
+    <t>010140.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
@@ -79,19 +82,13 @@
     <t>009540.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🤏 바닥권 접근 구간입니다.</t>
-  </si>
-  <si>
-    <t>🟠 하락 우위 (긴장 구간)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>124400</v>
+        <v>29250</v>
       </c>
       <c r="E2">
-        <v>45.8</v>
+        <v>55</v>
       </c>
       <c r="F2">
-        <v>-8.119999999999999</v>
+        <v>24.47</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="J2">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K2">
-        <v>42.1</v>
+        <v>49.2</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>403500</v>
+        <v>137300</v>
       </c>
       <c r="E3">
-        <v>53.3</v>
+        <v>53.8</v>
       </c>
       <c r="F3">
-        <v>-8.609999999999999</v>
+        <v>26.54</v>
       </c>
       <c r="G3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="J3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K3">
-        <v>39.7</v>
+        <v>46.2</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -587,10 +584,10 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>32.42054265786911</v>
+        <v>43.44936356612781</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,40 +601,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>27850</v>
+        <v>428500</v>
       </c>
       <c r="E4">
-        <v>49</v>
+        <v>58.1</v>
       </c>
       <c r="F4">
-        <v>-0.54</v>
+        <v>13.06</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H4">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4">
+        <v>46</v>
+      </c>
+      <c r="J4">
         <v>56</v>
       </c>
-      <c r="J4">
-        <v>80</v>
-      </c>
       <c r="K4">
-        <v>38.1</v>
+        <v>43.4</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>43.44936356612781</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>32.42054265786911</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -61,7 +61,10 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-11</t>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>HDKSOE</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
@@ -70,16 +73,13 @@
     <t>Hanwha Ocean</t>
   </si>
   <si>
-    <t>HDKSOE</t>
+    <t>009540.KS</t>
   </si>
   <si>
     <t>010140.KS</t>
   </si>
   <si>
     <t>042660.KS</t>
-  </si>
-  <si>
-    <t>009540.KS</t>
   </si>
   <si>
     <t>Pattern</t>
@@ -507,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>29250</v>
+        <v>425000</v>
       </c>
       <c r="E2">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="F2">
-        <v>24.47</v>
+        <v>4.42</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J2">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="K2">
-        <v>49.2</v>
+        <v>53.7</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -554,28 +554,28 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>137300</v>
+        <v>30850</v>
       </c>
       <c r="E3">
-        <v>53.8</v>
+        <v>56.2</v>
       </c>
       <c r="F3">
-        <v>26.54</v>
+        <v>13.42</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>53</v>
+      </c>
+      <c r="I3">
         <v>56</v>
       </c>
-      <c r="I3">
-        <v>53</v>
-      </c>
       <c r="J3">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>46.2</v>
+        <v>52.9</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -601,13 +601,13 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>428500</v>
+        <v>136700</v>
       </c>
       <c r="E4">
-        <v>58.1</v>
+        <v>47.8</v>
       </c>
       <c r="F4">
-        <v>13.06</v>
+        <v>11.96</v>
       </c>
       <c r="G4">
         <v>40</v>
@@ -616,13 +616,13 @@
         <v>63</v>
       </c>
       <c r="I4">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J4">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K4">
-        <v>43.4</v>
+        <v>45.7</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>43.44936356612781</v>
+        <v>41.74287521812095</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -537,7 +537,7 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -584,7 +584,7 @@
         <v>23</v>
       </c>
       <c r="N3">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -631,7 +631,7 @@
         <v>23</v>
       </c>
       <c r="N4">
-        <v>41.74287521812095</v>
+        <v>41.81508460778518</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,34 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-03-12</t>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
   </si>
   <si>
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
+    <t>010140.KS</t>
+  </si>
+  <si>
     <t>009540.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
     <t>042660.KS</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>📈 매수 관찰 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🟢 상승 우위 (다소 완화)</t>
   </si>
 </sst>
 </file>
@@ -507,28 +510,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>425000</v>
+        <v>28200</v>
       </c>
       <c r="E2">
-        <v>52.5</v>
+        <v>48.7</v>
       </c>
       <c r="F2">
-        <v>4.42</v>
+        <v>4.64</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="J2">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K2">
-        <v>53.7</v>
+        <v>61.4</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>30850</v>
+        <v>391500</v>
       </c>
       <c r="E3">
-        <v>56.2</v>
+        <v>44.7</v>
       </c>
       <c r="F3">
-        <v>13.42</v>
+        <v>5.1</v>
       </c>
       <c r="G3">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
         <v>60</v>
       </c>
-      <c r="H3">
-        <v>53</v>
-      </c>
-      <c r="I3">
-        <v>56</v>
-      </c>
       <c r="J3">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K3">
-        <v>52.9</v>
+        <v>59</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>136700</v>
+        <v>127600</v>
       </c>
       <c r="E4">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="F4">
-        <v>11.96</v>
+        <v>0.71</v>
       </c>
       <c r="G4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>63</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J4">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K4">
-        <v>45.7</v>
+        <v>59</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>41.81508460778518</v>
+        <v>66.57973643566133</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>날짜</t>
   </si>
@@ -61,37 +61,34 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-04-08</t>
+    <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>HDKSOE</t>
   </si>
   <si>
     <t>SamsungHvyInd</t>
   </si>
   <si>
-    <t>HDKSOE</t>
-  </si>
-  <si>
     <t>Hanwha Ocean</t>
   </si>
   <si>
+    <t>009540.KS</t>
+  </si>
+  <si>
     <t>010140.KS</t>
   </si>
   <si>
-    <t>009540.KS</t>
-  </si>
-  <si>
     <t>042660.KS</t>
   </si>
   <si>
     <t>Pattern</t>
   </si>
   <si>
-    <t>📈 매수 관찰 구간입니다.</t>
-  </si>
-  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>🟢 상승 우위 (다소 완화)</t>
+    <t>⚪ 중립 구간</t>
   </si>
 </sst>
 </file>
@@ -510,28 +507,28 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>28200</v>
+        <v>461500</v>
       </c>
       <c r="E2">
-        <v>48.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F2">
-        <v>4.64</v>
+        <v>-1.49</v>
       </c>
       <c r="G2">
         <v>50</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K2">
-        <v>61.4</v>
+        <v>56.7</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -540,10 +537,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>66.57973643566133</v>
+        <v>59.14876667115259</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -557,40 +554,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>391500</v>
+        <v>33150</v>
       </c>
       <c r="E3">
-        <v>44.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F3">
-        <v>5.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K3">
-        <v>59</v>
+        <v>54.9</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O3" t="s">
         <v>24</v>
-      </c>
-      <c r="N3">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -604,16 +601,16 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>127600</v>
+        <v>129100</v>
       </c>
       <c r="E4">
-        <v>48.1</v>
+        <v>56.4</v>
       </c>
       <c r="F4">
-        <v>0.71</v>
+        <v>-3.58</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>63</v>
@@ -622,22 +619,22 @@
         <v>60</v>
       </c>
       <c r="J4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K4">
-        <v>59</v>
+        <v>50.7</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4">
+        <v>59.14876667115259</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="N4">
-        <v>66.57973643566133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/DECISION/국장_조선_분석.xlsx
+++ b/DECISION/국장_조선_분석.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>날짜</t>
   </si>
@@ -61,34 +61,37 @@
     <t>MACRO_SIGNAL</t>
   </si>
   <si>
-    <t>2026-05-07</t>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>SamsungHvyInd</t>
+  </si>
+  <si>
+    <t>Hanwha Ocean</t>
   </si>
   <si>
     <t>HDKSOE</t>
   </si>
   <si>
-    <t>SamsungHvyInd</t>
-  </si>
-  <si>
-    <t>Hanwha Ocean</t>
+    <t>010140.KS</t>
+  </si>
+  <si>
+    <t>042660.KS</t>
   </si>
   <si>
     <t>009540.KS</t>
   </si>
   <si>
-    <t>010140.KS</t>
-  </si>
-  <si>
-    <t>042660.KS</t>
-  </si>
-  <si>
     <t>Pattern</t>
   </si>
   <si>
+    <t>🤏 바닥권 접근 구간입니다.</t>
+  </si>
+  <si>
     <t>⛔ 관망하십시오.</t>
   </si>
   <si>
-    <t>⚪ 중립 구간</t>
+    <t>🔴 강한 긴축 / 리스크</t>
   </si>
 </sst>
 </file>
@@ -507,19 +510,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>461500</v>
+        <v>27750</v>
       </c>
       <c r="E2">
-        <v>69.59999999999999</v>
+        <v>38.2</v>
       </c>
       <c r="F2">
-        <v>-1.49</v>
+        <v>-2.29</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I2">
         <v>60</v>
@@ -528,7 +531,7 @@
         <v>70</v>
       </c>
       <c r="K2">
-        <v>56.7</v>
+        <v>30.9</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -537,10 +540,10 @@
         <v>23</v>
       </c>
       <c r="N2">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -554,40 +557,40 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <v>33150</v>
+        <v>112200</v>
       </c>
       <c r="E3">
-        <v>72.59999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="F3">
-        <v>-0.6</v>
+        <v>-9.66</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>50</v>
+      </c>
+      <c r="J3">
         <v>63</v>
       </c>
-      <c r="I3">
-        <v>63</v>
-      </c>
-      <c r="J3">
-        <v>76</v>
-      </c>
       <c r="K3">
-        <v>54.9</v>
+        <v>29.9</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N3">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -601,40 +604,40 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>129100</v>
+        <v>379000</v>
       </c>
       <c r="E4">
-        <v>56.4</v>
+        <v>32.4</v>
       </c>
       <c r="F4">
-        <v>-3.58</v>
+        <v>-8.67</v>
       </c>
       <c r="G4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H4">
         <v>63</v>
       </c>
       <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
         <v>60</v>
       </c>
-      <c r="J4">
-        <v>70</v>
-      </c>
       <c r="K4">
-        <v>50.7</v>
+        <v>26.9</v>
       </c>
       <c r="L4" t="s">
         <v>22</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N4">
-        <v>59.14876667115259</v>
+        <v>13.11002090356014</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
